--- a/artfynd/A 58839-2025 artfynd.xlsx
+++ b/artfynd/A 58839-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56784783</v>
+        <v>126537899</v>
       </c>
       <c r="B2" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nybodkölen, Dlr</t>
+          <t>Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442587.1925972255</v>
+        <v>442522</v>
       </c>
       <c r="R2" t="n">
-        <v>6733482.923109335</v>
+        <v>6733610</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-10-09</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-10-09</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,65 +770,64 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121395776</v>
+        <v>126544883</v>
       </c>
       <c r="B3" t="n">
-        <v>78352</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>V Finngruvan, Dlr</t>
+          <t>Bötån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442592</v>
+        <v>442539</v>
       </c>
       <c r="R3" t="n">
-        <v>6733485</v>
+        <v>6733302</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -842,7 +836,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Malung-Sälen</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -852,17 +846,17 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Vänjan</t>
+          <t>Malung</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,68 +865,64 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121395752</v>
+        <v>126531391</v>
       </c>
       <c r="B4" t="n">
-        <v>78353</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>V Finngruvan, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442592</v>
+        <v>442584</v>
       </c>
       <c r="R4" t="n">
-        <v>6733485</v>
+        <v>6733316</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,12 +949,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,66 +984,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126317971</v>
+        <v>126531405</v>
       </c>
       <c r="B5" t="n">
-        <v>78738</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442667</v>
+        <v>442601</v>
       </c>
       <c r="R5" t="n">
-        <v>6733482</v>
+        <v>6733324</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,22 +1061,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,69 +1091,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126318186</v>
+        <v>126531438</v>
       </c>
       <c r="B6" t="n">
-        <v>78738</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>442671</v>
+        <v>442598</v>
       </c>
       <c r="R6" t="n">
-        <v>6733554</v>
+        <v>6733335</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1181,22 +1168,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1211,64 +1198,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126544883</v>
+        <v>126531473</v>
       </c>
       <c r="B7" t="n">
-        <v>96562</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bötån, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>442539</v>
+        <v>442562</v>
       </c>
       <c r="R7" t="n">
-        <v>6733302</v>
+        <v>6733341</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1277,7 +1260,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Malung-Sälen</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1287,7 +1270,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Malung</t>
+          <t>Vänjan</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1295,44 +1278,53 @@
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126533437</v>
+        <v>126531531</v>
       </c>
       <c r="B8" t="n">
-        <v>79011</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1356,14 +1348,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442752</v>
+        <v>442561</v>
       </c>
       <c r="R8" t="n">
-        <v>6733557</v>
+        <v>6733369</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1395,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1405,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,14 +1424,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126532413</v>
+        <v>126531704</v>
       </c>
       <c r="B9" t="n">
-        <v>79011</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1467,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442701</v>
+        <v>442580</v>
       </c>
       <c r="R9" t="n">
-        <v>6733473</v>
+        <v>6733390</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1512,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1539,14 +1531,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126532558</v>
+        <v>126531717</v>
       </c>
       <c r="B10" t="n">
-        <v>79011</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1570,17 +1562,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bötå böj, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442670</v>
+        <v>442581</v>
       </c>
       <c r="R10" t="n">
-        <v>6733482</v>
+        <v>6733384</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1609,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1619,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,26 +1626,26 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson, Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126532356</v>
+        <v>126531754</v>
       </c>
       <c r="B11" t="n">
-        <v>79011</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1681,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442672</v>
+        <v>442586</v>
       </c>
       <c r="R11" t="n">
-        <v>6733497</v>
+        <v>6733372</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1714,19 +1706,9 @@
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:44</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,14 +1735,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126533517</v>
+        <v>126532174</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1788,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442732</v>
+        <v>442587</v>
       </c>
       <c r="R12" t="n">
-        <v>6733607</v>
+        <v>6733482</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,7 +1805,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1833,7 +1815,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1860,14 +1842,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126531704</v>
+        <v>126532233</v>
       </c>
       <c r="B13" t="n">
-        <v>79011</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1895,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442580</v>
+        <v>442578</v>
       </c>
       <c r="R13" t="n">
-        <v>6733390</v>
+        <v>6733497</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1930,7 +1912,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1940,7 +1922,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1967,50 +1949,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126535521</v>
+        <v>126532344</v>
       </c>
       <c r="B14" t="n">
-        <v>8447</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442661</v>
+        <v>442669</v>
       </c>
       <c r="R14" t="n">
-        <v>6733562</v>
+        <v>6733498</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2042,7 +2019,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2052,7 +2029,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2079,14 +2056,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126533458</v>
+        <v>126532356</v>
       </c>
       <c r="B15" t="n">
-        <v>79011</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2110,14 +2087,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442754</v>
+        <v>442672</v>
       </c>
       <c r="R15" t="n">
-        <v>6733597</v>
+        <v>6733497</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2149,7 +2126,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2159,7 +2136,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2186,48 +2163,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126532432</v>
+        <v>126532363</v>
       </c>
       <c r="B16" t="n">
-        <v>78769</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bötå böj, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>442670</v>
+        <v>442675</v>
       </c>
       <c r="R16" t="n">
         <v>6733482</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2256,7 +2233,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2266,7 +2243,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2281,63 +2258,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126545006</v>
+        <v>126532387</v>
       </c>
       <c r="B17" t="n">
-        <v>79629</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bötå Böj, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442689</v>
+        <v>442679</v>
       </c>
       <c r="R17" t="n">
-        <v>6733596</v>
+        <v>6733494</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2364,44 +2338,53 @@
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126531531</v>
+        <v>126532413</v>
       </c>
       <c r="B18" t="n">
-        <v>79011</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2429,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442561</v>
+        <v>442701</v>
       </c>
       <c r="R18" t="n">
-        <v>6733369</v>
+        <v>6733473</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2464,7 +2447,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2474,7 +2457,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2501,48 +2484,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126532164</v>
+        <v>126532558</v>
       </c>
       <c r="B19" t="n">
-        <v>78769</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442589</v>
+        <v>442670</v>
       </c>
       <c r="R19" t="n">
         <v>6733482</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2569,9 +2552,19 @@
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2586,26 +2579,26 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126536000</v>
+        <v>126532998</v>
       </c>
       <c r="B20" t="n">
-        <v>79011</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2633,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>442621</v>
+        <v>442725</v>
       </c>
       <c r="R20" t="n">
-        <v>6733565</v>
+        <v>6733534</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2668,7 +2661,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2678,7 +2671,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2705,14 +2698,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126535429</v>
+        <v>126533027</v>
       </c>
       <c r="B21" t="n">
-        <v>79011</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2740,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>442676</v>
+        <v>442706</v>
       </c>
       <c r="R21" t="n">
-        <v>6733613</v>
+        <v>6733533</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2775,7 +2768,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2785,12 +2778,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2817,14 +2805,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126535381</v>
+        <v>126533418</v>
       </c>
       <c r="B22" t="n">
-        <v>79011</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2848,14 +2836,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>442681</v>
+        <v>442749</v>
       </c>
       <c r="R22" t="n">
-        <v>6733614</v>
+        <v>6733551</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2887,7 +2875,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2897,7 +2885,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2924,14 +2912,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126535340</v>
+        <v>126533437</v>
       </c>
       <c r="B23" t="n">
-        <v>79011</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2955,14 +2943,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>442705</v>
+        <v>442752</v>
       </c>
       <c r="R23" t="n">
-        <v>6733607</v>
+        <v>6733557</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2994,7 +2982,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3004,7 +2992,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3031,14 +3019,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126531391</v>
+        <v>126533458</v>
       </c>
       <c r="B24" t="n">
-        <v>79011</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3062,14 +3050,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>442584</v>
+        <v>442754</v>
       </c>
       <c r="R24" t="n">
-        <v>6733316</v>
+        <v>6733597</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3101,7 +3089,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3111,12 +3099,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:51</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3143,14 +3126,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126532174</v>
+        <v>126533468</v>
       </c>
       <c r="B25" t="n">
-        <v>79011</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3174,14 +3157,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>442587</v>
+        <v>442751</v>
       </c>
       <c r="R25" t="n">
-        <v>6733482</v>
+        <v>6733598</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3213,7 +3196,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3223,7 +3206,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3250,14 +3233,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126533506</v>
+        <v>126533495</v>
       </c>
       <c r="B26" t="n">
-        <v>79011</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3285,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>442734</v>
+        <v>442742</v>
       </c>
       <c r="R26" t="n">
-        <v>6733610</v>
+        <v>6733609</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3320,7 +3303,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3330,7 +3313,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3357,14 +3340,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126532998</v>
+        <v>126533506</v>
       </c>
       <c r="B27" t="n">
-        <v>79011</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3388,14 +3371,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>442725</v>
+        <v>442734</v>
       </c>
       <c r="R27" t="n">
-        <v>6733534</v>
+        <v>6733610</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3427,7 +3410,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3437,7 +3420,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3464,14 +3447,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126533495</v>
+        <v>126533508</v>
       </c>
       <c r="B28" t="n">
-        <v>79011</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3499,7 +3482,7 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>442742</v>
+        <v>442733</v>
       </c>
       <c r="R28" t="n">
         <v>6733609</v>
@@ -3534,7 +3517,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3544,7 +3527,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3571,45 +3554,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126533259</v>
+        <v>126533517</v>
       </c>
       <c r="B29" t="n">
-        <v>78770</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>442752</v>
+        <v>442732</v>
       </c>
       <c r="R29" t="n">
-        <v>6733552</v>
+        <v>6733607</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3641,7 +3624,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3651,7 +3634,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3678,14 +3661,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126533468</v>
+        <v>126533520</v>
       </c>
       <c r="B30" t="n">
-        <v>79011</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3709,14 +3692,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>442751</v>
+        <v>442732</v>
       </c>
       <c r="R30" t="n">
-        <v>6733598</v>
+        <v>6733605</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3748,7 +3731,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3758,7 +3741,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3785,14 +3768,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126533027</v>
+        <v>126535244</v>
       </c>
       <c r="B31" t="n">
-        <v>79011</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3820,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>442706</v>
+        <v>442724</v>
       </c>
       <c r="R31" t="n">
-        <v>6733533</v>
+        <v>6733608</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3855,7 +3838,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3865,7 +3848,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3892,14 +3875,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126532344</v>
+        <v>126535271</v>
       </c>
       <c r="B32" t="n">
-        <v>79011</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3927,10 +3910,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>442669</v>
+        <v>442720</v>
       </c>
       <c r="R32" t="n">
-        <v>6733498</v>
+        <v>6733609</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3962,7 +3945,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3972,7 +3955,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3999,14 +3982,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126535244</v>
+        <v>126535323</v>
       </c>
       <c r="B33" t="n">
-        <v>79011</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4034,10 +4017,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>442724</v>
+        <v>442705</v>
       </c>
       <c r="R33" t="n">
-        <v>6733608</v>
+        <v>6733607</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4069,7 +4052,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4079,7 +4062,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4106,14 +4089,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126535271</v>
+        <v>126535381</v>
       </c>
       <c r="B34" t="n">
-        <v>79011</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4141,10 +4124,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>442720</v>
+        <v>442681</v>
       </c>
       <c r="R34" t="n">
-        <v>6733609</v>
+        <v>6733614</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4176,7 +4159,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4186,7 +4169,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4213,14 +4196,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126531473</v>
+        <v>126535429</v>
       </c>
       <c r="B35" t="n">
-        <v>79011</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4248,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>442562</v>
+        <v>442676</v>
       </c>
       <c r="R35" t="n">
-        <v>6733341</v>
+        <v>6733613</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4283,7 +4266,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4293,7 +4276,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4320,14 +4308,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126531754</v>
+        <v>126536000</v>
       </c>
       <c r="B36" t="n">
-        <v>79011</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4355,10 +4343,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>442586</v>
+        <v>442621</v>
       </c>
       <c r="R36" t="n">
-        <v>6733372</v>
+        <v>6733565</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4388,9 +4376,19 @@
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4417,14 +4415,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126533520</v>
+        <v>126536090</v>
       </c>
       <c r="B37" t="n">
-        <v>79011</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4452,10 +4450,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>442732</v>
+        <v>442588</v>
       </c>
       <c r="R37" t="n">
-        <v>6733605</v>
+        <v>6733620</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4487,7 +4485,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4497,7 +4495,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4524,14 +4522,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126531405</v>
+        <v>126536348</v>
       </c>
       <c r="B38" t="n">
-        <v>79011</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4555,17 +4553,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>442601</v>
+        <v>442595</v>
       </c>
       <c r="R38" t="n">
-        <v>6733324</v>
+        <v>6733618</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4594,7 +4592,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4604,7 +4602,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4619,26 +4617,26 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126533508</v>
+        <v>126537753</v>
       </c>
       <c r="B39" t="n">
-        <v>79011</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4662,14 +4660,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>442733</v>
+        <v>442537</v>
       </c>
       <c r="R39" t="n">
-        <v>6733609</v>
+        <v>6733624</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4701,7 +4699,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4711,7 +4709,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4738,10 +4736,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126532233</v>
+        <v>121395776</v>
       </c>
       <c r="B40" t="n">
-        <v>79011</v>
+        <v>79084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4749,34 +4747,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>V Finngruvan, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>442578</v>
+        <v>442592</v>
       </c>
       <c r="R40" t="n">
-        <v>6733497</v>
+        <v>6733485</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4803,22 +4801,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>09:32</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>09:32</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4833,22 +4821,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126532387</v>
+        <v>126317971</v>
       </c>
       <c r="B41" t="n">
-        <v>79011</v>
+        <v>79084</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4856,34 +4844,43 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>442679</v>
+        <v>442667</v>
       </c>
       <c r="R41" t="n">
-        <v>6733494</v>
+        <v>6733482</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4910,22 +4907,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4940,22 +4937,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126533418</v>
+        <v>126318186</v>
       </c>
       <c r="B42" t="n">
-        <v>79011</v>
+        <v>79084</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4963,37 +4960,46 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>442749</v>
+        <v>442671</v>
       </c>
       <c r="R42" t="n">
-        <v>6733551</v>
+        <v>6733554</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5017,22 +5023,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5047,22 +5053,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126532363</v>
+        <v>126532164</v>
       </c>
       <c r="B43" t="n">
-        <v>79011</v>
+        <v>79084</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5070,21 +5076,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5094,7 +5100,7 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>442675</v>
+        <v>442589</v>
       </c>
       <c r="R43" t="n">
         <v>6733482</v>
@@ -5127,19 +5133,9 @@
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>09:46</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>09:46</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5166,53 +5162,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126533010</v>
+        <v>126532201</v>
       </c>
       <c r="B44" t="n">
-        <v>8447</v>
+        <v>79084</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>442722</v>
+        <v>442621</v>
       </c>
       <c r="R44" t="n">
-        <v>6733535</v>
+        <v>6733325</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5241,7 +5232,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5251,7 +5242,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5266,60 +5257,57 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson, Lars-Erik Nilsson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126533405</v>
+        <v>126532432</v>
       </c>
       <c r="B45" t="n">
-        <v>80018</v>
+        <v>79084</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kättbo besparingsskog, Dlr</t>
+          <t>Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>442740</v>
+        <v>442670</v>
       </c>
       <c r="R45" t="n">
-        <v>6733570</v>
+        <v>6733482</v>
       </c>
       <c r="S45" t="n">
         <v>2</v>
@@ -5351,7 +5339,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5361,12 +5349,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På gammal asp</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5375,7 +5358,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5394,10 +5376,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126531717</v>
+        <v>56784783</v>
       </c>
       <c r="B46" t="n">
-        <v>79011</v>
+        <v>79946</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5405,34 +5387,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Nybodkölen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>442581</v>
+        <v>442587</v>
       </c>
       <c r="R46" t="n">
-        <v>6733384</v>
+        <v>6733483</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5459,22 +5441,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>09:01</t>
+          <t>2013-10-09</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>09:01</t>
+          <t>2013-10-09</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5489,15 +5461,1795 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>126545006</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Bötå Böj, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>442689</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6733596</v>
+      </c>
+      <c r="S47" t="n">
+        <v>50</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>126533405</v>
+      </c>
+      <c r="B48" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Kättbo besparingsskog, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>442740</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6733570</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På gammal asp</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>126536536</v>
+      </c>
+      <c r="B49" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Bötå böj, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>442595</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6733618</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>126316384</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Bötå böj, Bötå böj, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>442653</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6733405</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>126536329</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Bötå böj, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>442595</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6733618</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Balning</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>126533010</v>
+      </c>
+      <c r="B52" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Bötå böj, Bötå böj, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>442722</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6733535</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>126533200</v>
+      </c>
+      <c r="B53" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>442746</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6733524</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>126535521</v>
+      </c>
+      <c r="B54" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Bötå böj, Bötå böj, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>442661</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6733562</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>126536970</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Bötå böj, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>442595</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6733618</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>126319566</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Bötå böj, Bötå böj, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>442470</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6733787</v>
+      </c>
+      <c r="S56" t="n">
+        <v>12</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>126536612</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Bötå böj, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>442595</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6733618</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>126537111</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Bötå böj, Bötå böj, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>442479</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6733796</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>121395752</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>V Finngruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>442592</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6733485</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>126531747</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Bötå böj, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>442621</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6733325</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>126533259</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>442752</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6733552</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>126536931</v>
+      </c>
+      <c r="B62" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Bötå böj, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>442595</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6733618</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
